--- a/jira_export_2026-09-21.xlsx
+++ b/jira_export_2026-09-21.xlsx
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>312 h</t>
+          <t>318 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P168"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -8264,7 +8264,7 @@
         <v>8</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>21</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>15.08</v>
+        <v>17.08</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
         <v>34</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L155" s="11" t="inlineStr"/>
       <c r="M155" s="11" t="inlineStr"/>
@@ -12385,18 +12385,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-668</t>
+          <t>PSC-1158</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DUGNY</t>
+          <t>COMMUNE DE PLERIN</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12413,14 +12413,14 @@
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L167" s="11" t="inlineStr"/>
       <c r="M167" s="11" t="inlineStr"/>
@@ -12435,31 +12435,83 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="17" t="inlineStr">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>PSC-668</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="C168" s="14" t="inlineStr"/>
+      <c r="D168" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE DUGNY</t>
+        </is>
+      </c>
+      <c r="E168" s="14" t="inlineStr"/>
+      <c r="F168" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H168" s="14" t="inlineStr"/>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K168" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L168" s="14" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+      <c r="N168" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B168" s="17" t="inlineStr"/>
-      <c r="C168" s="17" t="inlineStr"/>
-      <c r="D168" s="17" t="inlineStr"/>
-      <c r="E168" s="17" t="inlineStr"/>
-      <c r="F168" s="17" t="inlineStr"/>
-      <c r="G168" s="17" t="inlineStr"/>
-      <c r="H168" s="17" t="inlineStr"/>
-      <c r="I168" s="17" t="inlineStr"/>
-      <c r="J168" s="17" t="inlineStr"/>
-      <c r="K168" s="17" t="inlineStr"/>
-      <c r="L168" s="17" t="inlineStr"/>
-      <c r="M168" s="17" t="inlineStr"/>
-      <c r="N168" s="18" t="n">
+      <c r="B169" s="17" t="inlineStr"/>
+      <c r="C169" s="17" t="inlineStr"/>
+      <c r="D169" s="17" t="inlineStr"/>
+      <c r="E169" s="17" t="inlineStr"/>
+      <c r="F169" s="17" t="inlineStr"/>
+      <c r="G169" s="17" t="inlineStr"/>
+      <c r="H169" s="17" t="inlineStr"/>
+      <c r="I169" s="17" t="inlineStr"/>
+      <c r="J169" s="17" t="inlineStr"/>
+      <c r="K169" s="17" t="inlineStr"/>
+      <c r="L169" s="17" t="inlineStr"/>
+      <c r="M169" s="17" t="inlineStr"/>
+      <c r="N169" s="18" t="n">
         <v>48290.375</v>
       </c>
-      <c r="O168" s="18" t="n">
+      <c r="O169" s="18" t="n">
         <v>34861.488</v>
       </c>
-      <c r="P168" s="18" t="n">
-        <v>174.26</v>
+      <c r="P169" s="18" t="n">
+        <v>169.8</v>
       </c>
     </row>
   </sheetData>
@@ -12628,6 +12680,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13709,16 +13762,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>108.17</v>
+        <v>109.17</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>33.67</v>
+        <v>35.92</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>13.25</v>
+        <v>15.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>155.08</v>
+        <v>160.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22.92</v>
@@ -13728,7 +13781,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13823,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -13855,10 +13908,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>388506</v>
+        <v>391246</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>165454</v>
+        <v>168194</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>223052</v>
@@ -13880,10 +13933,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>170402</v>
+        <v>173142</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69638</v>
+        <v>72378</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>100764</v>
@@ -14948,7 +15001,7 @@
         </is>
       </c>
       <c r="I25" s="25" t="n">
-        <v>0</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="26">
@@ -15059,7 +15112,7 @@
         </is>
       </c>
       <c r="I28" s="24" t="n">
-        <v>52730</v>
+        <v>55470</v>
       </c>
     </row>
     <row r="29">
@@ -15080,7 +15133,7 @@
         </is>
       </c>
       <c r="I29" s="24" t="n">
-        <v>14880</v>
+        <v>17620</v>
       </c>
     </row>
     <row r="30">

--- a/jira_export_2026-09-21.xlsx
+++ b/jira_export_2026-09-21.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>34,861 €</t>
+          <t>34,960 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -770,7 +770,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>25,351 €</t>
+          <t>25,450 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>318 h</t>
+          <t>322 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>98.5</v>
+        <v>197</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>51</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
@@ -12508,10 +12508,10 @@
         <v>48290.375</v>
       </c>
       <c r="O169" s="18" t="n">
-        <v>34861.488</v>
+        <v>34959.988</v>
       </c>
       <c r="P169" s="18" t="n">
-        <v>169.8</v>
+        <v>169.45</v>
       </c>
     </row>
   </sheetData>
@@ -13774,7 +13774,7 @@
         <v>160.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>22.92</v>
+        <v>24.17</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>40.75</v>
+        <v>41.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -13801,7 +13801,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>5.5</v>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>83</v>
+        <v>84.5</v>
       </c>
     </row>
   </sheetData>
@@ -13908,19 +13908,19 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>391246</v>
+        <v>391148</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>168194</v>
+        <v>170601</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>223052</v>
+        <v>220547</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>135558</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>20728</v>
+        <v>18223</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>21338</v>
@@ -13958,19 +13958,19 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>218104</v>
+        <v>218006</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>95816</v>
+        <v>98222</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>122288</v>
+        <v>119783</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>49679</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>11553</v>
+        <v>9048</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>18153</v>
